--- a/ver3/tree.xlsx
+++ b/ver3/tree.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32.28515625" customWidth="1" style="9" min="1" max="1"/>
@@ -647,6 +647,11 @@
           <t>1886</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q280722</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="1" s="6">
       <c r="A4">
@@ -668,7 +673,16 @@
           <t>Ульянова</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Бланк_Александр_Дмитриевич</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Гроссшопф_Анна_Ивановна</t>
+        </is>
+      </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
           <t>1835</t>
@@ -691,7 +705,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>https://ru.ruwiki.ru/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0 ; https://ru.wikipedia.org/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0</t>
+          <t>https://ru.ruwiki.ru/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0 ; https://ru.wikipedia.org/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0 ; https://www.wikidata.org/wiki/Q470041</t>
         </is>
       </c>
     </row>
@@ -773,17 +787,377 @@
         <f>SUBSTITUTE(B7, " ", "_")</f>
         <v/>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Бланк Александр Дмитриевич</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q29474575</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="1" s="6">
       <c r="A8">
         <f>SUBSTITUTE(B8, " ", "_")</f>
         <v/>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Гроссшопф Анна Ивановна</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="1" s="6">
       <c r="A9">
         <f>SUBSTITUTE(B9, " ", "_")</f>
         <v/>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ульянова Анна Ильинична</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Елизарова</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ульянов_Илья_Николаевич</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Бланк_Мария_Александровна</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>14.08.1864</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>19.10.1935</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q4174883</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>SUBSTITUTE(B10, " ", "_")</f>
+        <v/>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ульянов Александр Ильич</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ульянов_Илья_Николаевич</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Бланк_Мария_Александровна</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>12.04.1866</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>20.05.1887</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q333241</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>SUBSTITUTE(B11, " ", "_")</f>
+        <v/>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ульянова Ольга Ильинична</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ульянов_Илья_Николаевич</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Бланк_Мария_Александровна</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q4475081</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>SUBSTITUTE(B12, " ", "_")</f>
+        <v/>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ульянов Дмитрий Ильич</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ульянов_Илья_Николаевич</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Бланк_Мария_Александровна</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1874</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1874</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1943</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1943</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1965609</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>SUBSTITUTE(B13, " ", "_")</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ульянова Мария Ильинична</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ульянов_Илья_Николаевич</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Бланк_Мария_Александровна</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>18.02.1878</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12.06.1937</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q4475079</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <f>SUBSTITUTE(B14, " ", "_")</f>
+        <v/>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Крупская Надежда Константиновна</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>14.02.1869</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>27.02.1939</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q215637</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -806,7 +1180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59.42578125" customWidth="1" style="9" min="1" max="1"/>
@@ -884,6 +1258,48 @@
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">25.08 (6.09) 1863 </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>B3&amp;"-"&amp;C3</f>
+        <v/>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Бланк_Александр_Дмитриевич</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Гроссшопф_Анна_Ивановна</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>B4&amp;"-"&amp;C4</f>
+        <v/>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ульянов_Владимир_Ильич</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Крупская_Надежда_Константиновна</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>22.07.1898</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Шушенское</t>
         </is>
       </c>
     </row>

--- a/ver3/tree.xlsx
+++ b/ver3/tree.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32.28515625" customWidth="1" style="9" min="1" max="1"/>
@@ -545,6 +545,26 @@
           <t>patronymic</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>birthPlace_</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>deathPlace_</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>burialPlace_</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>occupation_</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="1" s="6">
       <c r="A2">
@@ -601,6 +621,26 @@
           <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Симбирск</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Горки</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Мавзолей, Москва</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>революционер, политик</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="1" s="6">
       <c r="A3">
@@ -652,6 +692,21 @@
           <t>https://www.wikidata.org/wiki/Q280722</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Астрахань</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Симбирск</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>педагог, инспектор народных училищ</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="1" s="6">
       <c r="A4">
@@ -708,6 +763,21 @@
           <t>https://ru.ruwiki.ru/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0 ; https://ru.wikipedia.org/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0 ; https://www.wikidata.org/wiki/Q470041</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Петроград</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>учительница</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="1" s="6">
       <c r="A5">
@@ -745,6 +815,21 @@
           <t>1836</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Нижегородская губерния</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Астрахань</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>портной, мещанин</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="1" s="6">
       <c r="A6">
@@ -781,6 +866,21 @@
           <t>1871</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Астрахань</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Астрахань</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>домохозяйка</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="1" s="6">
       <c r="A7">
@@ -822,6 +922,21 @@
           <t>https://www.wikidata.org/wiki/Q29474575</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Староконстантинов</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Кокушкино</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>врач</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="1" s="6">
       <c r="A8">
@@ -858,6 +973,21 @@
           <t>1838</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Любек, Германия</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>домохозяйка</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="1" s="6">
       <c r="A9">
@@ -1157,6 +1287,413 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q215637</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ульянов Василий Николаевич</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ульянин_Николай_Васильевич</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Смирнова_Анна_Алексеевна</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>~1823</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>~1878</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>~1878</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>приказчик (управляющий соляным делом)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ульянова Мария Николаевна</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Горшкова</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ульянин_Николай_Васильевич</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Смирнова_Анна_Алексеевна</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>~1825</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>~1825</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>домохозяйка</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ульянова Феодосия Николаевна</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ульянин_Николай_Васильевич</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Смирнова_Анна_Алексеевна</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>~1827</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>~1827</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Бланк Дмитрий Александрович</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Бланк_Александр_Дмитриевич</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Гроссшопф_Анна_Ивановна</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>09.09.1830</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>19.01.1850</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Российская Империя</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>студент юридического факультета</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Бланк Анна Александровна</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Веретенникова</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Бланк_Александр_Дмитриевич</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Гроссшопф_Анна_Ивановна</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>30.08.1831</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>домохозяйка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Бланк Любовь Александровна</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ардашева/Пономарёва</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Бланк_Александр_Дмитриевич</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Гроссшопф_Анна_Ивановна</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>29.08.1832</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>домохозяйка</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Бланк Екатерина Александровна</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Залежская</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Бланк_Александр_Дмитриевич</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Гроссшопф_Анна_Ивановна</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>04.01.1834</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>домохозяйка</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Бланк Софья Александровна</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Лаврова</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Бланк_Александр_Дмитриевич</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Гроссшопф_Анна_Ивановна</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1836</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>24.07.1836</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>домохозяйка</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59.42578125" customWidth="1" style="9" min="1" max="1"/>
@@ -1239,6 +1776,16 @@
           <t>hyperLink_</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>childrenCount_</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>endReason_</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1260,6 +1807,16 @@
           <t xml:space="preserve">25.08 (6.09) 1863 </t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>смерть супруга</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -1276,6 +1833,16 @@
           <t>Гроссшопф_Анна_Ивановна</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>смерть супруги</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -1300,6 +1867,48 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>Шушенское</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>смерть супруга</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ульянин_Николай_Васильевич</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Смирнова_Анна_Алексеевна</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>~1823</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Астрахань</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>смерть супруга</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.7109375" customWidth="1" style="9" min="1" max="1"/>
@@ -3365,6 +3974,168 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>birthPlace_</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>место рождения</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>birthplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>deathPlace_</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>место смерти</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>place of death</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>burialPlace_</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>место захоронения</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>burial place</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>occupation_</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>профессия</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>occupation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>childrenCount_</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>число детей</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>children count</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>endReason_</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>причина окончания</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>end reason</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="0" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/ver3/tree.xlsx
+++ b/ver3/tree.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="foto_location" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="language" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="help" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <charset val="204"/>
@@ -73,6 +74,9 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -95,7 +99,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,6 +116,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -456,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32.28515625" customWidth="1" style="9" min="1" max="1"/>
@@ -565,6 +573,11 @@
           <t>occupation_</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>nationality_</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="1" s="6">
       <c r="A2">
@@ -1430,7 +1443,6 @@
           <t>1908</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -1717,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59.42578125" customWidth="1" style="9" min="1" max="1"/>
@@ -1784,6 +1796,11 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>endReason_</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>marriagePlace_</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.7109375" customWidth="1" style="9" min="1" max="1"/>
@@ -4136,8 +4153,1860 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nationality_</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Национальность</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>marriagePlace_</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Место брака</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Marriage place</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" style="9" min="1" max="1"/>
+    <col width="20" customWidth="1" style="9" min="2" max="2"/>
+    <col width="60" customWidth="1" style="9" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Лист (Sheet)</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Поле (Field)</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Описание (Description)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Лист персон (людей) семейного древа</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idA</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Уникальный идентификатор персоны (без пробелов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>label_</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Полное имя персоны (ФИО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Пол: М (мужской) или Ж (женский)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>surName2_</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Девичья фамилия (для женщин, вышедших замуж)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hasFather</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>idA отца персоны</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hasMother</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>idA матери персоны</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>birth</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Год рождения</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>birthFull_</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Полная дата рождения</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Год смерти</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>deathFull_</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Полная дата смерти</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>hyperLink_</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Ссылки на внешние источники (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>surName</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Фамилия</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>firstName</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>patronymic</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Отчество</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>birthPlace_</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Место рождения</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>deathPlace_</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Место смерти</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>burialPlace_</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Место захоронения</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>occupation_</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Род занятий, профессия</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nationality_</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Национальность</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Лист семей (браков)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>idA</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Уникальный идентификатор семьи</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>idA мужа</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>idA жены</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>marriage_</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Год заключения брака</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>marriagePlace_</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Место заключения брака</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>locationM_</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Основные места жизни семьи (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>divorce</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Год развода</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>locationD</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Место развода</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>label_</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Подпись семьи на диаграмме</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>hyperLink_</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Ссылки на внешние источники (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>childrenCount_</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Количество детей</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>endReason_</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Причина окончания брака</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Лист фотографий персон</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>id_person</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>idA персоны</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>suffix</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Суффикс файла (год фото)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Расширение файла (jpg, png)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>idA</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Имя файла фото (вычисляется автоматически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>title_</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Название/описание фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>location_</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Место съёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>date_</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Дата съёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>label_</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>Подпись к фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>hyperLink_</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Ссылка на источник фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Лист семейных фотографий</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>id_family</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>idA семьи</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>suffix_</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Суффикс файла (год фото)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Расширение файла</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>idA</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Имя файла фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>title_</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Название фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>inFamily</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>Кто из семьи на фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>inFoto</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Кто изображён на фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>full_person</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>Полный список персон</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>location_</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Место съёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>date_</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Дата съёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>person_label</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Подписи персон</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>label_</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Подпись к фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>hyperLink_</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Ссылка на источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>id_personAll</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Все idA персон на фото (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>Лист групповых фотографий</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>id_person</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>idA основной персоны</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>suffix_</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Суффикс файла</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>Расширение файла</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>idA</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Имя файла фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>title_</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Название фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>id_personAll</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>Все idA персон на фото (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>location_</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Место съёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>date_</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Дата съёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>person_label</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Подписи персон</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>label_</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Подпись к фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>hyperLink_</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>Ссылка на источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>Лист фотографий мест</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>id_loc</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Идентификатор места</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>suffix</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>Суффикс файла</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Расширение файла</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>idA</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>Имя файла фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>title_</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>Название места</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>locationGroup</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Группа мест</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>id_personAll</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>Связанные персоны (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>id_familyAll</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Связанные семьи (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>location_</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>Адрес/описание места</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>date_</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>Дата съёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>person_label</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>Подписи персон</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>label_</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>Подпись к фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>hyperLink_</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>Ссылка на источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>synonym_</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>Синонимы названия места</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>Лист событий</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>id_event</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>Идентификатор события</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>eventGroup</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>Группа/тип события</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>id_personAll</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>Участники события (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>id_familyAll</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>Связанные семьи (через ;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>title_</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Название события</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>location_</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Место события</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>date_</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>Дата события</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>person_label</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Подписи участников</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>label_</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>Описание события</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hyperLink_</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>Ссылки на источники</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>foto_person</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>Файл фото персоны</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>foto_family</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>Файл семейного фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>foto_group</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>Файл группового фото</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>foto_location</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>Файл фото места</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>Лист локализации (переводов полей)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>Тип записи</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>Название листа</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>Название поля (с суффиксом _)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>Перевод на русский</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Перевод на английский</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ver3/tree.xlsx
+++ b/ver3/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree\v4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo\6\family-tree-desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,15 @@
     <sheet name="language" sheetId="8" r:id="rId8"/>
     <sheet name="help" sheetId="9" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$22</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="346">
   <si>
     <t>idA</t>
   </si>
@@ -186,9 +189,6 @@
   </si>
   <si>
     <t>Ульянин Николай Васильевич</t>
-  </si>
-  <si>
-    <t>M</t>
   </si>
   <si>
     <t>1768</t>
@@ -1672,29 +1672,29 @@
         <v>52</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="G5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="O5" t="s">
         <v>55</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O5" t="s">
-        <v>56</v>
       </c>
       <c r="P5" t="s">
         <v>39</v>
       </c>
       <c r="R5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1703,22 +1703,22 @@
         <v>Смирнова_Анна_Алексеевна</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="O6" t="s">
         <v>39</v>
@@ -1727,7 +1727,7 @@
         <v>39</v>
       </c>
       <c r="R6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1736,16 +1736,16 @@
         <v>Бланк_Александр_Дмитриевич</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
         <v>24</v>
@@ -1754,16 +1754,16 @@
         <v>24</v>
       </c>
       <c r="K7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O7" t="s">
         <v>64</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>65</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
         <v>66</v>
-      </c>
-      <c r="R7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1772,31 +1772,31 @@
         <v>Гроссшопф_Анна_Ивановна</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="G8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
         <v>69</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>69</v>
       </c>
-      <c r="I8" t="s">
+      <c r="O8" t="s">
         <v>70</v>
       </c>
-      <c r="J8" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>71</v>
       </c>
-      <c r="P8" t="s">
-        <v>72</v>
-      </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1805,13 +1805,13 @@
         <v>Ульянова_Анна_Ильинична</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
@@ -1820,19 +1820,19 @@
         <v>23</v>
       </c>
       <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" t="s">
         <v>75</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>76</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>77</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>78</v>
-      </c>
-      <c r="K9" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1841,7 +1841,7 @@
         <v>Ульянов_Александр_Ильич</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -1853,19 +1853,19 @@
         <v>23</v>
       </c>
       <c r="G10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s">
         <v>81</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>82</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>83</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>84</v>
-      </c>
-      <c r="K10" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1874,7 +1874,7 @@
         <v>Ульянова_Ольга_Ильинична</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
@@ -1886,19 +1886,19 @@
         <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" t="s">
         <v>87</v>
-      </c>
-      <c r="J11" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1907,7 +1907,7 @@
         <v>Ульянов_Дмитрий_Ильич</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -1919,19 +1919,19 @@
         <v>23</v>
       </c>
       <c r="G12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" t="s">
         <v>90</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>90</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>91</v>
-      </c>
-      <c r="J12" t="s">
-        <v>91</v>
-      </c>
-      <c r="K12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1940,7 +1940,7 @@
         <v>Ульянова_Мария_Ильинична</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
@@ -1952,19 +1952,19 @@
         <v>23</v>
       </c>
       <c r="G13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" t="s">
         <v>94</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>95</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>96</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>97</v>
-      </c>
-      <c r="K13" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1973,25 +1973,25 @@
         <v>Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
         <v>42</v>
       </c>
       <c r="G14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" t="s">
         <v>100</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>101</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>102</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>103</v>
-      </c>
-      <c r="K14" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -2000,7 +2000,7 @@
         <v>Ульянов_Василий_Николаевич</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -2012,19 +2012,19 @@
         <v>35</v>
       </c>
       <c r="G15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" t="s">
         <v>106</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>107</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
+        <v>107</v>
+      </c>
+      <c r="R15" t="s">
         <v>108</v>
-      </c>
-      <c r="J15" t="s">
-        <v>108</v>
-      </c>
-      <c r="R15" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2033,13 +2033,13 @@
         <v>Ульянова_Мария_Николаевна</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
@@ -2048,19 +2048,19 @@
         <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2069,7 +2069,7 @@
         <v>Ульянова_Феодосия_Николаевна</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
         <v>42</v>
@@ -2081,16 +2081,16 @@
         <v>35</v>
       </c>
       <c r="G17" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" t="s">
         <v>114</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>114</v>
-      </c>
-      <c r="I17" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -2099,7 +2099,7 @@
         <v>Бланк_Дмитрий_Александрович</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -2111,25 +2111,25 @@
         <v>45</v>
       </c>
       <c r="G18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" t="s">
         <v>117</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>118</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>119</v>
       </c>
-      <c r="J18" t="s">
+      <c r="O18" t="s">
         <v>120</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>121</v>
       </c>
-      <c r="P18" t="s">
+      <c r="R18" t="s">
         <v>122</v>
-      </c>
-      <c r="R18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2138,13 +2138,13 @@
         <v>Бланк_Анна_Александровна</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
         <v>44</v>
@@ -2156,16 +2156,16 @@
         <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2174,13 +2174,13 @@
         <v>Бланк_Любовь_Александровна</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
         <v>44</v>
@@ -2189,19 +2189,19 @@
         <v>45</v>
       </c>
       <c r="G20" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" t="s">
         <v>129</v>
       </c>
-      <c r="H20" t="s">
-        <v>130</v>
-      </c>
       <c r="I20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2210,13 +2210,13 @@
         <v>Бланк_Екатерина_Александровна</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21" t="s">
         <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
         <v>44</v>
@@ -2225,19 +2225,19 @@
         <v>45</v>
       </c>
       <c r="G21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" t="s">
         <v>133</v>
       </c>
-      <c r="H21" t="s">
-        <v>134</v>
-      </c>
       <c r="I21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2246,13 +2246,13 @@
         <v>Бланк_Софья_Александровна</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
@@ -2261,22 +2261,23 @@
         <v>45</v>
       </c>
       <c r="G22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N22"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F9">
       <formula1>$A:$A</formula1>
@@ -2310,22 +2311,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2334,13 +2335,13 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K1" t="s">
         <v>144</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>145</v>
-      </c>
-      <c r="L1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2355,13 +2356,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J2" t="s">
         <v>147</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>148</v>
-      </c>
-      <c r="K2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2375,11 +2376,14 @@
       <c r="C3" t="s">
         <v>45</v>
       </c>
+      <c r="D3" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="J3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K3" t="s">
         <v>150</v>
-      </c>
-      <c r="K3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2388,22 +2392,22 @@
         <v>Ульянов_Владимир_Ильич-Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" t="s">
         <v>152</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>153</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>154</v>
       </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>155</v>
       </c>
-      <c r="J4" t="s">
-        <v>156</v>
-      </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2418,16 +2422,16 @@
         <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2459,25 +2463,25 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2488,26 +2492,26 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" t="s">
         <v>166</v>
-      </c>
-      <c r="I2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -2608,37 +2612,37 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -2647,25 +2651,25 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2">
         <v>1879</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Илья_Николаевич-Бланк_Мария_Александровна-1879.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -2674,13 +2678,13 @@
         <v>1879</v>
       </c>
       <c r="L2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M2" t="s">
         <v>177</v>
       </c>
-      <c r="M2" t="s">
-        <v>178</v>
-      </c>
       <c r="N2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -2762,31 +2766,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>1</v>
@@ -2797,68 +2801,68 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2">
         <v>1918</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1918.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" t="s">
         <v>179</v>
       </c>
-      <c r="F2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" t="s">
         <v>181</v>
       </c>
-      <c r="J2" t="s">
-        <v>182</v>
-      </c>
       <c r="K2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3">
         <v>1918</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Свердлов_Яков_Михайлович-1918.jpg</v>
       </c>
       <c r="E3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" t="s">
         <v>184</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>185</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="J3" t="s">
         <v>186</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="J3" t="s">
-        <v>187</v>
-      </c>
       <c r="K3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2945,37 +2949,37 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -2984,37 +2988,37 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s">
         <v>192</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>193</v>
-      </c>
-      <c r="C2" t="s">
-        <v>194</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L2" s="9"/>
       <c r="N2" t="s">
@@ -3047,28 +3051,28 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3077,60 +3081,60 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" t="s">
         <v>203</v>
       </c>
-      <c r="C2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I2" t="s">
         <v>204</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>205</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>206</v>
-      </c>
-      <c r="M2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" t="s">
         <v>208</v>
       </c>
-      <c r="C3" t="s">
-        <v>209</v>
-      </c>
       <c r="E3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" t="s">
         <v>179</v>
-      </c>
-      <c r="F3" t="s">
-        <v>180</v>
       </c>
       <c r="G3" s="4"/>
       <c r="M3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N3" t="s">
         <v>210</v>
-      </c>
-      <c r="N3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -3213,19 +3217,19 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3237,767 +3241,767 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" t="s">
         <v>217</v>
-      </c>
-      <c r="B2" t="s">
-        <v>218</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" t="s">
         <v>219</v>
-      </c>
-      <c r="E2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" t="s">
         <v>217</v>
-      </c>
-      <c r="B3" t="s">
-        <v>218</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" t="s">
         <v>221</v>
-      </c>
-      <c r="E3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" t="s">
         <v>217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>218</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" t="s">
         <v>223</v>
-      </c>
-      <c r="E4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" t="s">
         <v>217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>218</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" t="s">
         <v>225</v>
-      </c>
-      <c r="E5" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" t="s">
         <v>217</v>
-      </c>
-      <c r="B6" t="s">
-        <v>218</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" t="s">
         <v>227</v>
-      </c>
-      <c r="E6" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" t="s">
         <v>229</v>
       </c>
-      <c r="C7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>230</v>
-      </c>
-      <c r="E7" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E8" t="s">
         <v>232</v>
-      </c>
-      <c r="E8" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E9" t="s">
         <v>234</v>
-      </c>
-      <c r="E9" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" t="s">
         <v>227</v>
-      </c>
-      <c r="E10" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" t="s">
         <v>236</v>
-      </c>
-      <c r="E11" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" t="s">
         <v>232</v>
-      </c>
-      <c r="E12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" t="s">
         <v>238</v>
-      </c>
-      <c r="E13" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E14" t="s">
         <v>234</v>
-      </c>
-      <c r="E14" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" t="s">
         <v>227</v>
-      </c>
-      <c r="E15" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s">
+        <v>235</v>
+      </c>
+      <c r="E16" t="s">
         <v>236</v>
-      </c>
-      <c r="E16" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D17" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" t="s">
         <v>232</v>
-      </c>
-      <c r="E17" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D18" t="s">
+        <v>237</v>
+      </c>
+      <c r="E18" t="s">
         <v>238</v>
-      </c>
-      <c r="E18" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
+        <v>233</v>
+      </c>
+      <c r="E19" t="s">
         <v>234</v>
-      </c>
-      <c r="E19" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" t="s">
         <v>227</v>
-      </c>
-      <c r="E20" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D21" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" t="s">
         <v>236</v>
-      </c>
-      <c r="E21" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" t="s">
         <v>232</v>
-      </c>
-      <c r="E22" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D23" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" t="s">
         <v>238</v>
-      </c>
-      <c r="E23" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" t="s">
         <v>234</v>
-      </c>
-      <c r="E24" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" t="s">
         <v>227</v>
-      </c>
-      <c r="E25" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" t="s">
         <v>236</v>
-      </c>
-      <c r="E26" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D27" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" t="s">
         <v>232</v>
-      </c>
-      <c r="E27" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D28" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" t="s">
         <v>238</v>
-      </c>
-      <c r="E28" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29" t="s">
         <v>234</v>
-      </c>
-      <c r="E29" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" t="s">
         <v>227</v>
-      </c>
-      <c r="E30" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D31" t="s">
+        <v>239</v>
+      </c>
+      <c r="E31" t="s">
         <v>240</v>
-      </c>
-      <c r="E31" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" t="s">
         <v>236</v>
-      </c>
-      <c r="E32" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D33" t="s">
+        <v>231</v>
+      </c>
+      <c r="E33" t="s">
         <v>232</v>
-      </c>
-      <c r="E33" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D34" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" t="s">
         <v>238</v>
-      </c>
-      <c r="E34" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" t="s">
         <v>234</v>
-      </c>
-      <c r="E35" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
         <v>227</v>
-      </c>
-      <c r="E36" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" t="s">
         <v>217</v>
-      </c>
-      <c r="B39" t="s">
-        <v>218</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" t="s">
         <v>244</v>
-      </c>
-      <c r="E39" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" t="s">
         <v>217</v>
-      </c>
-      <c r="B40" t="s">
-        <v>218</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" t="s">
         <v>246</v>
-      </c>
-      <c r="E40" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>216</v>
+      </c>
+      <c r="B41" t="s">
         <v>217</v>
-      </c>
-      <c r="B41" t="s">
-        <v>218</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
+        <v>247</v>
+      </c>
+      <c r="E41" t="s">
         <v>248</v>
-      </c>
-      <c r="E41" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>216</v>
+      </c>
+      <c r="B42" t="s">
         <v>217</v>
-      </c>
-      <c r="B42" t="s">
-        <v>218</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" t="s">
         <v>250</v>
-      </c>
-      <c r="E42" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D43" t="s">
+        <v>251</v>
+      </c>
+      <c r="E43" t="s">
         <v>252</v>
-      </c>
-      <c r="E43" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D44" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" t="s">
         <v>254</v>
-      </c>
-      <c r="E44" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B45" t="s">
         <v>217</v>
-      </c>
-      <c r="B45" t="s">
-        <v>218</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
+        <v>255</v>
+      </c>
+      <c r="E45" t="s">
         <v>256</v>
-      </c>
-      <c r="E45" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D46" t="s">
+        <v>257</v>
+      </c>
+      <c r="E46" t="s">
         <v>258</v>
-      </c>
-      <c r="E46" t="s">
-        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -4017,1155 +4021,1155 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>261</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B54" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B69" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B73" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B75" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B77" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B78" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B82" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B88" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B89" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B90" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B91" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B92" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B93" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B94" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B95" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B98" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B99" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B100" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B101" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>339</v>
+      </c>
+      <c r="C102" s="11" t="s">
         <v>340</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B103" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B107" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/ver3/tree.xlsx
+++ b/ver3/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo\6\family-tree-desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo\6\family-tree-desktop_6_03\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25230" windowHeight="8235" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="352">
   <si>
     <t>idA</t>
   </si>
@@ -221,9 +221,6 @@
     <t>1804</t>
   </si>
   <si>
-    <t>https://www.wikidata.org/wiki/Q29474575</t>
-  </si>
-  <si>
     <t>Староконстантинов</t>
   </si>
   <si>
@@ -1068,6 +1065,27 @@
   </si>
   <si>
     <t>Перевод на английский</t>
+  </si>
+  <si>
+    <t>17.07.1870</t>
+  </si>
+  <si>
+    <t>https://www.wikidata.org/wiki/Q29474575 ; https://ru.wikipedia.org/wiki/%D0%A1%D0%B5%D0%BC%D1%8C%D1%8F_%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D1%8B%D1%85#%D0%9C%D0%B0%D1%82%D0%B5%D1%80%D0%B8%D0%BD%D1%81%D0%BA%D0%B0%D1%8F_%D0%BB%D0%B8%D0%BD%D0%B8%D1%8F</t>
+  </si>
+  <si>
+    <t>Эссен Екатерина Ивановна</t>
+  </si>
+  <si>
+    <t>https://www.famhist.ru/famhist/lenin_b/0003cac9.htm</t>
+  </si>
+  <si>
+    <t>Эссен_Екатерина_Ивановна</t>
+  </si>
+  <si>
+    <t>10.04.1841 </t>
+  </si>
+  <si>
+    <t>https://proza.ru/2025/03/17/154 ; https://zwiahel.ucoz.ru/novograd/evrei/lenin_01.html</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1170,6 +1188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1451,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" style="7" customWidth="1"/>
@@ -1530,7 +1549,7 @@
     </row>
     <row r="2" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A22" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <f t="shared" ref="A2:A23" si="0">SUBSTITUTE(B2, " ", "_")</f>
         <v>Ульянов_Владимир_Ильич</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1632,7 +1651,7 @@
       <c r="D4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F4" t="s">
@@ -1744,26 +1763,26 @@
       <c r="G7" t="s">
         <v>62</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="4" t="s">
         <v>62</v>
       </c>
       <c r="I7" t="s">
         <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>345</v>
       </c>
       <c r="K7" t="s">
+        <v>346</v>
+      </c>
+      <c r="O7" t="s">
         <v>63</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>64</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
         <v>65</v>
-      </c>
-      <c r="R7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1772,28 +1791,28 @@
         <v>Гроссшопф_Анна_Ивановна</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
         <v>68</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>68</v>
       </c>
-      <c r="I8" t="s">
+      <c r="O8" t="s">
         <v>69</v>
       </c>
-      <c r="J8" t="s">
-        <v>69</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>70</v>
-      </c>
-      <c r="P8" t="s">
-        <v>71</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1805,13 +1824,13 @@
         <v>Ульянова_Анна_Ильинична</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
@@ -1820,19 +1839,19 @@
         <v>23</v>
       </c>
       <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>75</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>76</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>77</v>
-      </c>
-      <c r="K9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1841,7 +1860,7 @@
         <v>Ульянов_Александр_Ильич</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -1853,19 +1872,19 @@
         <v>23</v>
       </c>
       <c r="G10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>81</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>82</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>83</v>
-      </c>
-      <c r="K10" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1874,7 +1893,7 @@
         <v>Ульянова_Ольга_Ильинична</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
@@ -1888,17 +1907,17 @@
       <c r="G11" t="s">
         <v>59</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="4" t="s">
         <v>59</v>
       </c>
       <c r="I11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" t="s">
         <v>86</v>
-      </c>
-      <c r="J11" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1907,7 +1926,7 @@
         <v>Ульянов_Дмитрий_Ильич</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -1919,19 +1938,19 @@
         <v>23</v>
       </c>
       <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" t="s">
         <v>89</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>89</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>90</v>
-      </c>
-      <c r="J12" t="s">
-        <v>90</v>
-      </c>
-      <c r="K12" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1940,7 +1959,7 @@
         <v>Ульянова_Мария_Ильинична</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
@@ -1952,19 +1971,19 @@
         <v>23</v>
       </c>
       <c r="G13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>94</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>95</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>96</v>
-      </c>
-      <c r="K13" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1973,25 +1992,25 @@
         <v>Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
         <v>42</v>
       </c>
       <c r="G14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>100</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>101</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>102</v>
-      </c>
-      <c r="K14" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -2000,7 +2019,7 @@
         <v>Ульянов_Василий_Николаевич</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -2012,19 +2031,19 @@
         <v>35</v>
       </c>
       <c r="G15" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>106</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
+        <v>106</v>
+      </c>
+      <c r="R15" t="s">
         <v>107</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R15" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2033,13 +2052,13 @@
         <v>Ульянова_Мария_Николаевна</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
@@ -2048,16 +2067,16 @@
         <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R16" t="s">
         <v>60</v>
@@ -2069,7 +2088,7 @@
         <v>Ульянова_Феодосия_Николаевна</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
         <v>42</v>
@@ -2081,16 +2100,16 @@
         <v>35</v>
       </c>
       <c r="G17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" t="s">
         <v>113</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>113</v>
-      </c>
-      <c r="I17" t="s">
-        <v>114</v>
-      </c>
-      <c r="J17" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -2099,7 +2118,7 @@
         <v>Бланк_Дмитрий_Александрович</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -2111,25 +2130,25 @@
         <v>45</v>
       </c>
       <c r="G18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>117</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>118</v>
       </c>
-      <c r="J18" t="s">
+      <c r="O18" t="s">
         <v>119</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>120</v>
       </c>
-      <c r="P18" t="s">
+      <c r="R18" t="s">
         <v>121</v>
-      </c>
-      <c r="R18" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2138,13 +2157,13 @@
         <v>Бланк_Анна_Александровна</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
         <v>44</v>
@@ -2155,14 +2174,14 @@
       <c r="G19" t="s">
         <v>36</v>
       </c>
-      <c r="H19" t="s">
-        <v>125</v>
+      <c r="H19" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="I19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R19" t="s">
         <v>60</v>
@@ -2174,13 +2193,13 @@
         <v>Бланк_Любовь_Александровна</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
         <v>44</v>
@@ -2189,16 +2208,16 @@
         <v>45</v>
       </c>
       <c r="G20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H20" t="s">
-        <v>129</v>
-      </c>
       <c r="I20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R20" t="s">
         <v>60</v>
@@ -2210,13 +2229,13 @@
         <v>Бланк_Екатерина_Александровна</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
         <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
         <v>44</v>
@@ -2225,16 +2244,16 @@
         <v>45</v>
       </c>
       <c r="G21" t="s">
+        <v>131</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H21" t="s">
-        <v>133</v>
-      </c>
       <c r="I21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R21" t="s">
         <v>60</v>
@@ -2246,13 +2265,13 @@
         <v>Бланк_Софья_Александровна</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
@@ -2263,22 +2282,40 @@
       <c r="G22" t="s">
         <v>54</v>
       </c>
-      <c r="H22" t="s">
-        <v>136</v>
+      <c r="H22" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="I22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R22" t="s">
         <v>60</v>
       </c>
     </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Эссен_Екатерина_Ивановна</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1863</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N22"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F9">
       <formula1>$A:$A</formula1>
     </dataValidation>
@@ -2293,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.42578125" style="7" customWidth="1"/>
@@ -2311,22 +2348,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2335,13 +2372,13 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" t="s">
         <v>143</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>144</v>
-      </c>
-      <c r="L1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2356,13 +2393,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J2" t="s">
         <v>146</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>147</v>
-      </c>
-      <c r="K2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2377,13 +2414,13 @@
         <v>45</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K3" t="s">
         <v>149</v>
-      </c>
-      <c r="K3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2392,22 +2429,22 @@
         <v>Ульянов_Владимир_Ильич-Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" t="s">
         <v>151</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>152</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>153</v>
       </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>154</v>
       </c>
-      <c r="J4" t="s">
-        <v>155</v>
-      </c>
       <c r="K4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2422,16 +2459,34 @@
         <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
         <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K5" t="s">
-        <v>148</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="str">
+        <f>B6&amp;"-"&amp;C6</f>
+        <v>Бланк_Александр_Дмитриевич-Эссен_Екатерина_Ивановна</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -2463,25 +2518,25 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2492,26 +2547,26 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" t="s">
         <v>165</v>
-      </c>
-      <c r="I2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -2612,37 +2667,37 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -2651,25 +2706,25 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B2">
         <v>1879</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Илья_Николаевич-Бланк_Мария_Александровна-1879.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I2" t="s">
         <v>29</v>
@@ -2678,13 +2733,13 @@
         <v>1879</v>
       </c>
       <c r="L2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M2" t="s">
         <v>176</v>
       </c>
-      <c r="M2" t="s">
-        <v>177</v>
-      </c>
       <c r="N2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -2766,31 +2821,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>1</v>
@@ -2801,68 +2856,68 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2">
         <v>1918</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1918.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" t="s">
         <v>178</v>
       </c>
-      <c r="F2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" t="s">
         <v>180</v>
       </c>
-      <c r="J2" t="s">
-        <v>181</v>
-      </c>
       <c r="K2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B3">
         <v>1918</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Свердлов_Яков_Михайлович-1918.jpg</v>
       </c>
       <c r="E3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" t="s">
         <v>183</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>184</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="J3" t="s">
         <v>185</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" t="s">
-        <v>186</v>
-      </c>
       <c r="K3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2949,37 +3004,37 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -2988,37 +3043,37 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" t="s">
         <v>191</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>192</v>
-      </c>
-      <c r="C2" t="s">
-        <v>193</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L2" s="9"/>
       <c r="N2" t="s">
@@ -3051,28 +3106,28 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3081,60 +3136,60 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" t="s">
         <v>202</v>
       </c>
-      <c r="C2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2" t="s">
         <v>203</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>204</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>205</v>
-      </c>
-      <c r="M2" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" t="s">
         <v>207</v>
       </c>
-      <c r="C3" t="s">
-        <v>208</v>
-      </c>
       <c r="E3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" t="s">
         <v>178</v>
-      </c>
-      <c r="F3" t="s">
-        <v>179</v>
       </c>
       <c r="G3" s="4"/>
       <c r="M3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N3" t="s">
         <v>209</v>
-      </c>
-      <c r="N3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -3217,19 +3272,19 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3241,767 +3296,767 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" t="s">
         <v>216</v>
-      </c>
-      <c r="B2" t="s">
-        <v>217</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" t="s">
         <v>218</v>
-      </c>
-      <c r="E2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" t="s">
         <v>216</v>
-      </c>
-      <c r="B3" t="s">
-        <v>217</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" t="s">
         <v>220</v>
-      </c>
-      <c r="E3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" t="s">
         <v>216</v>
-      </c>
-      <c r="B4" t="s">
-        <v>217</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" t="s">
         <v>222</v>
-      </c>
-      <c r="E4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" t="s">
         <v>216</v>
-      </c>
-      <c r="B5" t="s">
-        <v>217</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" t="s">
         <v>224</v>
-      </c>
-      <c r="E5" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" t="s">
         <v>216</v>
-      </c>
-      <c r="B6" t="s">
-        <v>217</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" t="s">
         <v>226</v>
-      </c>
-      <c r="E6" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" t="s">
         <v>228</v>
       </c>
-      <c r="C7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>229</v>
-      </c>
-      <c r="E7" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" t="s">
         <v>231</v>
-      </c>
-      <c r="E8" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" t="s">
         <v>233</v>
-      </c>
-      <c r="E9" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" t="s">
         <v>226</v>
-      </c>
-      <c r="E10" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" t="s">
         <v>235</v>
-      </c>
-      <c r="E11" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E12" t="s">
         <v>231</v>
-      </c>
-      <c r="E12" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" t="s">
         <v>237</v>
-      </c>
-      <c r="E13" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E14" t="s">
         <v>233</v>
-      </c>
-      <c r="E14" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" t="s">
         <v>226</v>
-      </c>
-      <c r="E15" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D16" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" t="s">
         <v>235</v>
-      </c>
-      <c r="E16" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D17" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17" t="s">
         <v>231</v>
-      </c>
-      <c r="E17" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D18" t="s">
+        <v>236</v>
+      </c>
+      <c r="E18" t="s">
         <v>237</v>
-      </c>
-      <c r="E18" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E19" t="s">
         <v>233</v>
-      </c>
-      <c r="E19" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" t="s">
         <v>226</v>
-      </c>
-      <c r="E20" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E21" t="s">
         <v>235</v>
-      </c>
-      <c r="E21" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D22" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" t="s">
         <v>231</v>
-      </c>
-      <c r="E22" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D23" t="s">
+        <v>236</v>
+      </c>
+      <c r="E23" t="s">
         <v>237</v>
-      </c>
-      <c r="E23" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" t="s">
         <v>233</v>
-      </c>
-      <c r="E24" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" t="s">
         <v>226</v>
-      </c>
-      <c r="E25" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E26" t="s">
         <v>235</v>
-      </c>
-      <c r="E26" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D27" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27" t="s">
         <v>231</v>
-      </c>
-      <c r="E27" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D28" t="s">
+        <v>236</v>
+      </c>
+      <c r="E28" t="s">
         <v>237</v>
-      </c>
-      <c r="E28" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
+        <v>232</v>
+      </c>
+      <c r="E29" t="s">
         <v>233</v>
-      </c>
-      <c r="E29" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E30" t="s">
         <v>226</v>
-      </c>
-      <c r="E30" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D31" t="s">
+        <v>238</v>
+      </c>
+      <c r="E31" t="s">
         <v>239</v>
-      </c>
-      <c r="E31" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D32" t="s">
+        <v>234</v>
+      </c>
+      <c r="E32" t="s">
         <v>235</v>
-      </c>
-      <c r="E32" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" t="s">
         <v>231</v>
-      </c>
-      <c r="E33" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D34" t="s">
+        <v>236</v>
+      </c>
+      <c r="E34" t="s">
         <v>237</v>
-      </c>
-      <c r="E34" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B35" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
+        <v>232</v>
+      </c>
+      <c r="E35" t="s">
         <v>233</v>
-      </c>
-      <c r="E35" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
+        <v>225</v>
+      </c>
+      <c r="E36" t="s">
         <v>226</v>
-      </c>
-      <c r="E36" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" t="s">
         <v>216</v>
-      </c>
-      <c r="B39" t="s">
-        <v>217</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
+        <v>242</v>
+      </c>
+      <c r="E39" t="s">
         <v>243</v>
-      </c>
-      <c r="E39" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" t="s">
         <v>216</v>
-      </c>
-      <c r="B40" t="s">
-        <v>217</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
+        <v>244</v>
+      </c>
+      <c r="E40" t="s">
         <v>245</v>
-      </c>
-      <c r="E40" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s">
         <v>216</v>
-      </c>
-      <c r="B41" t="s">
-        <v>217</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" t="s">
         <v>247</v>
-      </c>
-      <c r="E41" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" t="s">
         <v>216</v>
-      </c>
-      <c r="B42" t="s">
-        <v>217</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
+        <v>248</v>
+      </c>
+      <c r="E42" t="s">
         <v>249</v>
-      </c>
-      <c r="E42" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" t="s">
         <v>251</v>
-      </c>
-      <c r="E43" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s">
+        <v>252</v>
+      </c>
+      <c r="E44" t="s">
         <v>253</v>
-      </c>
-      <c r="E44" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" t="s">
         <v>216</v>
-      </c>
-      <c r="B45" t="s">
-        <v>217</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
+        <v>254</v>
+      </c>
+      <c r="E45" t="s">
         <v>255</v>
-      </c>
-      <c r="E45" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D46" t="s">
+        <v>256</v>
+      </c>
+      <c r="E46" t="s">
         <v>257</v>
-      </c>
-      <c r="E46" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4021,1155 +4076,1155 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B78" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B82" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B86" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B89" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B91" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B92" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B93" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B98" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B99" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B100" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B101" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>338</v>
+      </c>
+      <c r="C102" s="11" t="s">
         <v>339</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B106" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
